--- a/DOSSIES_MULTIFORMATO/CGE/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/CGE/dossie.xlsx
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020NE00307</t>
+          <t>2020NE00304</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>377.6</v>
+        <v>878.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -677,14 +677,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anulação Parcial do Saldo da NE 2020NE00210, CT nº 003/2020 - CGE, em cumprimento ao Decreto nº 43.042, de 18 de novembro de 2020, publicado no DOE nº 34.376. (Encerramento do Exercício).</t>
+          <t>Anulação Total do Saldo da NE 2020NE00220, 2TA ao CT nº 003/2017 - CGE, em cumprimento ao Decreto nº 43.042, de 18 de novembro de 2020, publicado no DOE nº 34.376. (Encerramento do Exercício).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020NE00305</t>
+          <t>2020NE00306</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48767.17</v>
+        <v>17810.29</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -703,14 +703,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anulação Parcial do Saldo da NE 2020NE00278, 3TA ao CT nº 003/2017 - CGE, em cumprimento ao Decreto nº 43.042, de 18 de novembro de 2020, publicado no DOE nº 34.376. (Encerramento do Exercício).</t>
+          <t>Anulação Total do Saldo da NE 2020NE00221, 2TA ao CT nº 003/2017 - CGE, em cumprimento ao Decreto nº 43.042, de 18 de novembro de 2020, publicado no DOE nº 34.376. (Encerramento do Exercício).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020NE00306</t>
+          <t>2020NE00305</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17810.29</v>
+        <v>48767.17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -729,14 +729,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anulação Total do Saldo da NE 2020NE00221, 2TA ao CT nº 003/2017 - CGE, em cumprimento ao Decreto nº 43.042, de 18 de novembro de 2020, publicado no DOE nº 34.376. (Encerramento do Exercício).</t>
+          <t>Anulação Parcial do Saldo da NE 2020NE00278, 3TA ao CT nº 003/2017 - CGE, em cumprimento ao Decreto nº 43.042, de 18 de novembro de 2020, publicado no DOE nº 34.376. (Encerramento do Exercício).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020NE00304</t>
+          <t>2020NE00307</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>878.4</v>
+        <v>377.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -755,14 +755,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anulação Total do Saldo da NE 2020NE00220, 2TA ao CT nº 003/2017 - CGE, em cumprimento ao Decreto nº 43.042, de 18 de novembro de 2020, publicado no DOE nº 34.376. (Encerramento do Exercício).</t>
+          <t>Anulação Parcial do Saldo da NE 2020NE00210, CT nº 003/2020 - CGE, em cumprimento ao Decreto nº 43.042, de 18 de novembro de 2020, publicado no DOE nº 34.376. (Encerramento do Exercício).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2019NE00357</t>
+          <t>2019NE00356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42646.24</v>
+        <v>196946.71</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anulação Total do Saldo da NE 000315/2019,2TA CT. Nº003/2017-CGE, em cumprimento ao Decreto nº 41.554, de 26 de novembro de 2019. Publicado no DOE Nº 34.131 DE 26/11/2019. (Encerramento do exercício).</t>
+          <t>Anulação Total do Saldo da NE 000004/2019,1TA CT. Nº003/2017-CGE, em cumprimento ao Decreto nº 41.554, de 26 de novembro de 2019. Publicado no DOE Nº 34.131 DE 26/11/2019. (Encerramento do exercício).</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2019NE00356</t>
+          <t>2019NE00357</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>196946.71</v>
+        <v>42646.24</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anulação Total do Saldo da NE 000004/2019,1TA CT. Nº003/2017-CGE, em cumprimento ao Decreto nº 41.554, de 26 de novembro de 2019. Publicado no DOE Nº 34.131 DE 26/11/2019. (Encerramento do exercício).</t>
+          <t>Anulação Total do Saldo da NE 000315/2019,2TA CT. Nº003/2017-CGE, em cumprimento ao Decreto nº 41.554, de 26 de novembro de 2019. Publicado no DOE Nº 34.131 DE 26/11/2019. (Encerramento do exercício).</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2017NE00199</t>
+          <t>2017NE00201</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>144.11</v>
+        <v>3115.58</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -911,14 +911,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE nº 0061/2017, TA nº04 CT nº002/2012-CGE, em cumprimento a IN. nº001/2017-GSEFAZ de 12/12/2017, publicado no DOE nº 33.663 de 14/12/2017. ( encerramento do exercício).</t>
+          <t>Anulação total do saldo da NE nº 0181/2017, CT nº03/2017-CGE, em cumprimento a IN. nº001/2017-GSEFAZ de 12/12/2017, publicado no DOE nº 33.663 de 14/12/2017. ( encerramento do exercício).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2017NE00374</t>
+          <t>2017NE00200</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2445.6</v>
+        <v>37952.88</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -937,14 +937,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da Nota de Empenho nº 2017NE00102, correspondente ao 1º TA-CT.002/2016-OGE, para ajuste orçamentário no encerramento do exercício.</t>
+          <t>Anulação total do saldo da NE nº 0180/2017, CT nº03/2017-CGE, em cumprimento a IN. nº001/2017-GSEFAZ de 12/12/2017, publicado no DOE nº 33.663 de 14/12/2017. ( encerramento do exercício).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2017NE00200</t>
+          <t>2017NE00199</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37952.88</v>
+        <v>144.11</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -963,14 +963,14 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE nº 0180/2017, CT nº03/2017-CGE, em cumprimento a IN. nº001/2017-GSEFAZ de 12/12/2017, publicado no DOE nº 33.663 de 14/12/2017. ( encerramento do exercício).</t>
+          <t>Anulação total do saldo da NE nº 0061/2017, TA nº04 CT nº002/2012-CGE, em cumprimento a IN. nº001/2017-GSEFAZ de 12/12/2017, publicado no DOE nº 33.663 de 14/12/2017. ( encerramento do exercício).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2017NE00201</t>
+          <t>2017NE00374</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3115.58</v>
+        <v>2445.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE nº 0181/2017, CT nº03/2017-CGE, em cumprimento a IN. nº001/2017-GSEFAZ de 12/12/2017, publicado no DOE nº 33.663 de 14/12/2017. ( encerramento do exercício).</t>
+          <t>Anulação do Saldo da Nota de Empenho nº 2017NE00102, correspondente ao 1º TA-CT.002/2016-OGE, para ajuste orçamentário no encerramento do exercício.</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2022NE0000236</t>
+          <t>2022NE0000235</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1167.84</v>
+        <v>20000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado - CGE. (Conforme Projeto Básico)</t>
+          <t>REFORÇO QUE SE FAZ DA NE Nº 20 - PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A - REFERENTE AO QUARTO TERMO ADITIVO AO CONTRATO Nº 003/2017</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2022NE0000235</t>
+          <t>2022NE0000236</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>20000</v>
+        <v>1167.84</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>REFORÇO QUE SE FAZ DA NE Nº 20 - PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A - REFERENTE AO QUARTO TERMO ADITIVO AO CONTRATO Nº 003/2017</t>
+          <t>Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado - CGE. (Conforme Projeto Básico)</t>
         </is>
       </c>
     </row>
@@ -1314,17 +1314,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2023NE0000098</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>2023NE0000101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>25/04/2023</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>126919.84</v>
+        <v>2424.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1333,7 +1337,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>REFORÇO QUE SE FAZ DA NE 029/2023 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO (TI), PARA ATENDER AS NECESSIDADES DA CONTROLADORIA GERAL DO ESATDO - REF.</t>
+          <t xml:space="preserve">Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado -CGE. Demais informações no Projeto Básico, páginas 32 a 35 - SIGED. TC: 003/2020 AD: </t>
         </is>
       </c>
     </row>
@@ -1370,21 +1374,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2023NE0000101</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3/2020</t>
-        </is>
-      </c>
+          <t>2023NE0000098</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>25/04/2023</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2424.2</v>
+        <v>126919.84</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1393,19 +1393,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado -CGE. Demais informações no Projeto Básico, páginas 32 a 35 - SIGED. TC: 003/2020 AD: </t>
+          <t>REFORÇO QUE SE FAZ DA NE 029/2023 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO (TI), PARA ATENDER AS NECESSIDADES DA CONTROLADORIA GERAL DO ESATDO - REF.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2019NE00075</t>
+          <t>2019NE00077</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>124006.32</v>
+        <v>3887.41</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prestação de Serviços de TI, tipo DESENVOLVIMENTO DE SISTEMA DE INFORMAÇÃO, conforme projeto básico.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Rede, compreendendo o acesso gerenciado à internet através da Rede de Governo, para a CONTROLADORIA-GERAL DO ESTADO.</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2019NE00077</t>
+          <t>2019NE00075</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3887.41</v>
+        <v>124006.32</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Rede, compreendendo o acesso gerenciado à internet através da Rede de Governo, para a CONTROLADORIA-GERAL DO ESTADO.</t>
+          <t>Contratação de empresa especializada em prestação de Serviços de TI, tipo DESENVOLVIMENTO DE SISTEMA DE INFORMAÇÃO, conforme projeto básico.</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024NE0000136</t>
+          <t>2024NE0000135</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15351.96</v>
+        <v>47748.88</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1543,19 +1543,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Rede, compreendendo o ACESSO GERENCIADO A REDE MUNDIAL DE INTERNET, para atender a CGE/AM. Demais informações no Projeto Básico (SIGED)</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE. Demais informações no Projeto Básic</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024NE0000135</t>
+          <t>2024NE0000136</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>47748.88</v>
+        <v>15351.96</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE. Demais informações no Projeto Básic</t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Rede, compreendendo o ACESSO GERENCIADO A REDE MUNDIAL DE INTERNET, para atender a CGE/AM. Demais informações no Projeto Básico (SIGED)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2022NE0000302</t>
+          <t>2022NE0000303</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>350.35</v>
+        <v>1970.13</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DO 2º TA AO CONTRATO Nº 003/2020-CGE, PRODAM S.A. ENCERRAMENTO DO EXERCÍCIO 2022. DECRETO Nº 46.621 DE 11/11/2022.</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DO 4º TA AO CONTRATO Nº 003/2017-CGE, PRODAM S.A. ENCERRAMENTO DO EXERCÍCIO 2022. DECRETO Nº 46.621 DE 11/11/2022.</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2022NE0000303</t>
+          <t>2022NE0000302</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1970.13</v>
+        <v>350.35</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DO 4º TA AO CONTRATO Nº 003/2017-CGE, PRODAM S.A. ENCERRAMENTO DO EXERCÍCIO 2022. DECRETO Nº 46.621 DE 11/11/2022.</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DO 2º TA AO CONTRATO Nº 003/2020-CGE, PRODAM S.A. ENCERRAMENTO DO EXERCÍCIO 2022. DECRETO Nº 46.621 DE 11/11/2022.</t>
         </is>
       </c>
     </row>
@@ -1718,14 +1718,10 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020NE00264</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1/2018</t>
-        </is>
-      </c>
+          <t>2020NE00263</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>23/11/2020</t>
@@ -1741,17 +1737,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 216-2020, REFERENTE AO 2º TA AO CTA Nº 001/2018-CGE (COMPLEMENTO)</t>
+          <t>ANULAÇÃO PARCIAL DA NE 210-2020, PARA CORREÇÃO</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2020NE00263</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>2020NE00264</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1/2018</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>23/11/2020</t>
@@ -1767,19 +1767,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 210-2020, PARA CORREÇÃO</t>
+          <t>REFORÇO DA NE 216-2020, REFERENTE AO 2º TA AO CTA Nº 001/2018-CGE (COMPLEMENTO)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2017NE00342</t>
+          <t>2017NE00344</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8565.34</v>
+        <v>1573.54</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1797,19 +1797,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE Nº 102 - PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 002/2016 VIGÊNCIA: 01/03/2017 A 01/03/2018 VALOR MENSAL: R$ 8.565,34 VALOR GLOBAL: R$ 102.784,08 FUNDAMENTO LEGAL: DISPENSA DE LICITAÇÃO, D</t>
+          <t>REFORÇO A NOTA DE EMPENHO Nº 205/2017.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2017NE00344</t>
+          <t>2017NE00342</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1573.54</v>
+        <v>8565.34</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1827,14 +1827,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>REFORÇO A NOTA DE EMPENHO Nº 205/2017.</t>
+          <t>REFORÇO DA NE Nº 102 - PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 002/2016 VIGÊNCIA: 01/03/2017 A 01/03/2018 VALOR MENSAL: R$ 8.565,34 VALOR GLOBAL: R$ 102.784,08 FUNDAMENTO LEGAL: DISPENSA DE LICITAÇÃO, D</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2016NE00025</t>
+          <t>2016NE00026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1864,7 +1864,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2016NE00026</t>
+          <t>2016NE00025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1894,7 +1894,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2023NE0000351</t>
+          <t>2023NE0000355</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2746.1</v>
+        <v>121.16</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1913,14 +1913,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DA NE 95-2023, REF. AO SEGUNDO TERMO ADITIVO AO CTA 002-2021, CONFORME DECRETO N° 48.363, DE 27.10.2023.</t>
+          <t xml:space="preserve">ANULAÇÃO PARCIAL DO SALDO DA NE 29-2023, REF. AO TERMO DE CTA 001-2023, CONFORME DECRETO N° 48.363, DE 27.10.2023. OBS: SUPRESSÃO DE 24,76% (VINTE E QUATRO VIRGULA SETENTA E SEIS POR CENTO), CONFORME </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2023NE0000350</t>
+          <t>2023NE0000354</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>713.45</v>
+        <v>85.08</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1939,14 +1939,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DA NE 56-2023, REF. AO SEGUNDO TERMO ADITIVO AO CTA 002-2021, CONFORME DECRETO N° 48.363, DE 27.10.2023.</t>
+          <t>ANULAÇÃO PARCIAL DO SALDO DA NE 56-2023, REF. AO SEGUNDO TERMO ADITIVO AO CTA 002-2021, CONFORME DECRETO N° 48.363, DE 27.10.2023. OBS: SUPRESSÃO DE 15,96% (QUINZE VIRGULA NOVENTA E SEIS POR CENTO), C</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2023NE0000352</t>
+          <t>2023NE0000353</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2023NE0000353</t>
+          <t>2023NE0000352</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2023NE0000354</t>
+          <t>2023NE0000350</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>85.08</v>
+        <v>713.45</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2017,14 +2017,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DO SALDO DA NE 56-2023, REF. AO SEGUNDO TERMO ADITIVO AO CTA 002-2021, CONFORME DECRETO N° 48.363, DE 27.10.2023. OBS: SUPRESSÃO DE 15,96% (QUINZE VIRGULA NOVENTA E SEIS POR CENTO), C</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DA NE 56-2023, REF. AO SEGUNDO TERMO ADITIVO AO CTA 002-2021, CONFORME DECRETO N° 48.363, DE 27.10.2023.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2023NE0000355</t>
+          <t>2023NE0000351</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>121.16</v>
+        <v>2746.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANULAÇÃO PARCIAL DO SALDO DA NE 29-2023, REF. AO TERMO DE CTA 001-2023, CONFORME DECRETO N° 48.363, DE 27.10.2023. OBS: SUPRESSÃO DE 24,76% (VINTE E QUATRO VIRGULA SETENTA E SEIS POR CENTO), CONFORME </t>
+          <t>ANULAÇÃO TOTAL DO SALDO DA NE 95-2023, REF. AO SEGUNDO TERMO ADITIVO AO CTA 002-2021, CONFORME DECRETO N° 48.363, DE 27.10.2023.</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2019NE00206</t>
+          <t>2019NE00217</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>200000</v>
+        <v>242.96</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2095,14 +2095,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>ANULAÇÃO QUE SE FAZ DEVIDO AO ENCERRAMENTO DO CONTRATO</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2019NE00217</t>
+          <t>2019NE00206</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>242.96</v>
+        <v>200000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2121,14 +2121,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ANULAÇÃO QUE SE FAZ DEVIDO AO ENCERRAMENTO DO CONTRATO</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2023NE00056</t>
+          <t>2023NE0000056</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2151,14 +2151,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2º T.A Contrato 002/2021 Prazo e Reajuste 1,86%</t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Rede, compreendendo o ACESSO GERENCIADO A REDE MUNDIAL DE INTERNET, para atender a CGE/AM. Demais informações no Projeto Básico (SIGED)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2023NE0000056</t>
+          <t>2023NE00056</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Rede, compreendendo o ACESSO GERENCIADO A REDE MUNDIAL DE INTERNET, para atender a CGE/AM. Demais informações no Projeto Básico (SIGED)</t>
+          <t>2º T.A Contrato 002/2021 Prazo e Reajuste 1,86%</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2018NE00336</t>
+          <t>2018NE00330</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1922.81</v>
+        <v>3887.41</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2267,14 +2267,14 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE00295, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE00114, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2018NE00328</t>
+          <t>2018NE00341</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1685</v>
+        <v>253326.52</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2293,14 +2293,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE0066, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE00067, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2018NE00340</t>
+          <t>2018NE00335</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1470.37</v>
+        <v>41335.44</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE00066, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE00294, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2018NE00335</t>
+          <t>2018NE00340</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>41335.44</v>
+        <v>1470.37</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE00294, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE00066, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2018NE00341</t>
+          <t>2018NE00328</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>253326.52</v>
+        <v>1685</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2397,14 +2397,14 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE00067, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO PARCIAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE0066, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2018NE00330</t>
+          <t>2018NE00336</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3887.41</v>
+        <v>1922.81</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE00114, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DA NOTA DE EMPENHO Nº 2018NE00295, PARA FINS DE AJUSTE ORÇAMENTÁRIO NO ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020NE00220</t>
+          <t>2020NE00221</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12425.03</v>
+        <v>42646.24</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2ºTA AO CT. Nº003/2017,REFERENTE SISTEMA DE GESTOR DE CONTEÚDO WEB-GERWE E LICENÇA DO PORTAL DA TRANSPARÊNCIA. OBS: TROCA DE FONTE DE RECURSO (145 PARA 100).</t>
+          <t>2º TA AO CT. Nº 003/2017, REFERENTE A PRESTAÇÃO DE SERVIÇO DE TI. OBS: TROCA DE FONTE DE RECURSO (145 PARA 100).</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020NE00221</t>
+          <t>2020NE00220</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>42646.24</v>
+        <v>12425.03</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2º TA AO CT. Nº 003/2017, REFERENTE A PRESTAÇÃO DE SERVIÇO DE TI. OBS: TROCA DE FONTE DE RECURSO (145 PARA 100).</t>
+          <t>2ºTA AO CT. Nº003/2017,REFERENTE SISTEMA DE GESTOR DE CONTEÚDO WEB-GERWE E LICENÇA DO PORTAL DA TRANSPARÊNCIA. OBS: TROCA DE FONTE DE RECURSO (145 PARA 100).</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2017NE00181</t>
+          <t>2017NE00180</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3115.58</v>
+        <v>37952.88</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2017NE00180</t>
+          <t>2017NE00181</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>37952.88</v>
+        <v>3115.58</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2786,17 +2786,21 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2020NE00204</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>2020NE00210</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>14/09/2020</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>85292.48</v>
+        <v>5609.99</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2805,14 +2809,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 006-2020, EM VIRTUDE DA TROCA DE FONTE (145 PARA A 100)</t>
+          <t>CONTRATAÇÃO DE PESSOA JURÍDICA PARA PRESTAÇÃO DE SERVIÇO DE PROTOCOLO SPROWEB, PARA A CGE-AM</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2020NE00203</t>
+          <t>2020NE00202</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2822,7 +2826,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12425.03</v>
+        <v>6823.7</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2831,7 +2835,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 001-2020, EM VIRTUDE DA TROCA DE FONTE (145 PARA A 100)</t>
+          <t>ANULAÇÃO PARCIAL DA NE 70-2020, EM VIRTUDE DA TROCA DE FONTE (145 PARA A 100)</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2868,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2020NE00202</t>
+          <t>2020NE00203</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -2874,7 +2878,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6823.7</v>
+        <v>12425.03</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2883,28 +2887,24 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 70-2020, EM VIRTUDE DA TROCA DE FONTE (145 PARA A 100)</t>
+          <t>ANULAÇÃO PARCIAL DA NE 001-2020, EM VIRTUDE DA TROCA DE FONTE (145 PARA A 100)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2020NE00210</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>3/2020</t>
-        </is>
-      </c>
+          <t>2020NE00204</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>14/09/2020</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5609.99</v>
+        <v>85292.48</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PESSOA JURÍDICA PARA PRESTAÇÃO DE SERVIÇO DE PROTOCOLO SPROWEB, PARA A CGE-AM</t>
+          <t>ANULAÇÃO TOTAL DA NE 006-2020, EM VIRTUDE DA TROCA DE FONTE (145 PARA A 100)</t>
         </is>
       </c>
     </row>
@@ -2950,14 +2950,10 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2020NE00125</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1/2018</t>
-        </is>
-      </c>
+          <t>2020NE00123</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
           <t>13/05/2020</t>
@@ -2973,17 +2969,21 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Contratação de Empresa para a prestação de serviços de rede, compreendendo o Acesso Gerenciado à rede mundial para a CGE/AM</t>
+          <t>ANULAÇÃO QUE SE FAZ PARA CORREÇÃO DE DESCRIÇÃO</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2020NE00123</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>2020NE00125</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1/2018</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>13/05/2020</t>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ANULAÇÃO QUE SE FAZ PARA CORREÇÃO DE DESCRIÇÃO</t>
+          <t>Contratação de Empresa para a prestação de serviços de rede, compreendendo o Acesso Gerenciado à rede mundial para a CGE/AM</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2021NE0000056</t>
+          <t>2021NE0000057</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>35188.74</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3141,19 +3141,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA A PRESTAÇÃO DE SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO À REDE MUNDIAL DE INTERNET PARA A CGE/AM.</t>
+          <t>REFORÇO QUE SE FAZ PARA COMPLEMENTO DO 2º T. A. AO CTA Nº 001/2018-CGE</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2021NE0000057</t>
+          <t>2021NE0000056</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>99.59999999999999</v>
+        <v>35188.74</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>REFORÇO QUE SE FAZ PARA COMPLEMENTO DO 2º T. A. AO CTA Nº 001/2018-CGE</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA A PRESTAÇÃO DE SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO À REDE MUNDIAL DE INTERNET PARA A CGE/AM.</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2022NE0000192</t>
+          <t>2022NE0000191</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2335.68</v>
+        <v>18160.52</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado - CGE. (Conforme Projeto Básico)</t>
+          <t>Contratação de Empresa Especializada na Prestação de Serviços de Rede, compreendendo o ACESSO GERENCIADO A REDE MUNDIAL DE INTERNET, para a CGE/AM. Conforme Projeto Básico.</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3414,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2022NE0000191</t>
+          <t>2022NE0000192</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>18160.52</v>
+        <v>2335.68</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação de Serviços de Rede, compreendendo o ACESSO GERENCIADO A REDE MUNDIAL DE INTERNET, para a CGE/AM. Conforme Projeto Básico.</t>
+          <t>Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado - CGE. (Conforme Projeto Básico)</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2018NE00075</t>
+          <t>2018NE00073</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4848.4</v>
+        <v>1642.29</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3497,19 +3497,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pagamento em favor da PRODAM SA, referente ao mês de DEZEMBRO/2017 - (2018RD00007).</t>
+          <t>Pagamento em favor da PRODAM SA, referente ao mês de DEZEMBRO/2017 - (2018RD00008).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2018NE00076</t>
+          <t>2018NE00074</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1573.54</v>
+        <v>2071.05</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3527,19 +3527,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pagamento em favor da PRODAM SA, referente ao mês de DEZEMBRO/2017 - (2018RD00004).</t>
+          <t>Pagamento em favor da PRODAM SA, referente ao mês de DEZEMBRO/2017 - (2018RD00006).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2018NE00074</t>
+          <t>2018NE00076</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2071.05</v>
+        <v>1573.54</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3557,19 +3557,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pagamento em favor da PRODAM SA, referente ao mês de DEZEMBRO/2017 - (2018RD00006).</t>
+          <t>Pagamento em favor da PRODAM SA, referente ao mês de DEZEMBRO/2017 - (2018RD00004).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2018NE00073</t>
+          <t>2018NE00075</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1642.29</v>
+        <v>4848.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pagamento em favor da PRODAM SA, referente ao mês de DEZEMBRO/2017 - (2018RD00008).</t>
+          <t>Pagamento em favor da PRODAM SA, referente ao mês de DEZEMBRO/2017 - (2018RD00007).</t>
         </is>
       </c>
     </row>
@@ -3860,17 +3860,21 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2018NE00065</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>2018NE00066</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
           <t>07/02/2018</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>34271.38</v>
+        <v>18693.48</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3879,28 +3883,24 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Anulação total da Nota de Empenho nº 2018NE00039, para mudança na Natureza de Despesa, em atenção à Orientação Técnica nº 12/2018-GINS/SEFAZ.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2018NE00067</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2018NE00064</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
           <t>07/02/2018</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>391991.12</v>
+        <v>417481.68</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3909,24 +3909,28 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE.</t>
+          <t>Anulação total da Nota de Empenho nº 2018NE00040, para mudança na Natureza de Despesa, em atenção à Orientação Técnica nº 12/2018-GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2018NE00064</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>2018NE00067</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
           <t>07/02/2018</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>417481.68</v>
+        <v>391991.12</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3935,28 +3939,24 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anulação total da Nota de Empenho nº 2018NE00040, para mudança na Natureza de Despesa, em atenção à Orientação Técnica nº 12/2018-GINS/SEFAZ.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2018NE00066</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2018NE00065</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
           <t>07/02/2018</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>18693.48</v>
+        <v>34271.38</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3965,14 +3965,14 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE.</t>
+          <t>Anulação total da Nota de Empenho nº 2018NE00039, para mudança na Natureza de Despesa, em atenção à Orientação Técnica nº 12/2018-GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2018NE00294</t>
+          <t>2018NE00295</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>41335.44</v>
+        <v>3393.18</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prestação de Serviços de TI, tipo DESENVOLVIMENTO DE SISTEMA DE INFORMAÇÃO, conforme projeto básico.</t>
+          <t>Contratação de empresa especializada em prestação de Serviços de TI, tipo LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - GESTOR DE CONTEÚDO WEB; e LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - PORTAL DA TRANSP</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2018NE00295</t>
+          <t>2018NE00294</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3393.18</v>
+        <v>41335.44</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prestação de Serviços de TI, tipo LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - GESTOR DE CONTEÚDO WEB; e LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - PORTAL DA TRANSP</t>
+          <t>Contratação de empresa especializada em prestação de Serviços de TI, tipo DESENVOLVIMENTO DE SISTEMA DE INFORMAÇÃO, conforme projeto básico.</t>
         </is>
       </c>
     </row>
@@ -4114,12 +4114,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025NE0000060</t>
+          <t>2025NE0000061</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>100835.42</v>
+        <v>11513.97</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE. Demais informações no Projeto Básic</t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Rede, compreendendo o ACESSO GERENCIADO A REDE MUNDIAL DE INTERNET, para atender a CGE/AM. Demais informações no Projeto Básico (SIGED)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025NE0000061</t>
+          <t>2025NE0000060</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11513.97</v>
+        <v>100835.42</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4167,19 +4167,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Rede, compreendendo o ACESSO GERENCIADO A REDE MUNDIAL DE INTERNET, para atender a CGE/AM. Demais informações no Projeto Básico (SIGED)</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE. Demais informações no Projeto Básic</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2023NE0000228</t>
+          <t>2023NE0000230</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2424.2</v>
+        <v>18268.22</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado -CGE. Demais informações no Projeto Básico, páginas 32 a 35 - SIGED. TC: 003/2020 AD: </t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Rede, compreendendo o ACESSO GERENCIADO A REDE MUNDIAL DE INTERNET, para atender a CGE/AM. Demais informações no Projeto Básico (SIGED)</t>
         </is>
       </c>
     </row>
@@ -4234,12 +4234,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2023NE0000230</t>
+          <t>2023NE0000228</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>18268.22</v>
+        <v>2424.2</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Rede, compreendendo o ACESSO GERENCIADO A REDE MUNDIAL DE INTERNET, para atender a CGE/AM. Demais informações no Projeto Básico (SIGED)</t>
+          <t xml:space="preserve">Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado -CGE. Demais informações no Projeto Básico, páginas 32 a 35 - SIGED. TC: 003/2020 AD: </t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2015NE00054</t>
+          <t>2015NE00017</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6/2012</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>24972.51</v>
+        <v>1248.72</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4377,19 +4377,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARA CORREÇÃO NA DESCRIÇÃO</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2015NE00017</t>
+          <t>2015NE00052</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1248.72</v>
+        <v>126982.32</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4407,14 +4407,14 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2015NE00057</t>
+          <t>2015NE00047</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4437,14 +4437,14 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>EMPENHO DE SERVIÇO</t>
+          <t>SEGUNDO TERMO ADITIVO AO CONTRATO Nº 006/2012 - SERVIÇO DE LINK DE ACESSO A INTERNET NO PAC MANACAPURU</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2015NE00047</t>
+          <t>2015NE00057</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4467,19 +4467,19 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SEGUNDO TERMO ADITIVO AO CONTRATO Nº 006/2012 - SERVIÇO DE LINK DE ACESSO A INTERNET NO PAC MANACAPURU</t>
+          <t>EMPENHO DE SERVIÇO</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2015NE00052</t>
+          <t>2015NE00054</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>6/2012</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>126982.32</v>
+        <v>24972.51</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
+          <t>ANULAÇÃO PARA CORREÇÃO NA DESCRIÇÃO</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2023NE0000160</t>
+          <t>2023NE0000159</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>63459.92</v>
+        <v>2424.2</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE. Demais informações no Projeto Básic</t>
+          <t xml:space="preserve">Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado -CGE. Demais informações no Projeto Básico, páginas 32 a 35 - SIGED. TC: 003/2020 AD: </t>
         </is>
       </c>
     </row>
@@ -4590,12 +4590,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2023NE0000159</t>
+          <t>2023NE0000160</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2424.2</v>
+        <v>63459.92</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado -CGE. Demais informações no Projeto Básico, páginas 32 a 35 - SIGED. TC: 003/2020 AD: </t>
+          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE. Demais informações no Projeto Básic</t>
         </is>
       </c>
     </row>
@@ -4650,21 +4650,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2021NE0000001</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>3/2020</t>
-        </is>
-      </c>
+          <t>2021NE0000005</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
           <t>04/01/2021</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2183</v>
+        <v>27337.6</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4673,24 +4669,28 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Contratação do Sistema de Protocolo – SPROWEB para atender a Controladoria-Geral do Estado.</t>
+          <t>Contratação de Empresa para a prestação de serviços de rede, compreendendo o Acesso Gerenciado à rede mundial para a CGE/AM</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2021NE0000005</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>2021NE0000001</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>3/2020</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr">
         <is>
           <t>04/01/2021</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>27337.6</v>
+        <v>2183</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Contratação de Empresa para a prestação de serviços de rede, compreendendo o Acesso Gerenciado à rede mundial para a CGE/AM</t>
+          <t>Contratação do Sistema de Protocolo – SPROWEB para atender a Controladoria-Geral do Estado.</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2021NE0000128</t>
+          <t>2021NE0000130</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>2/2021</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>5436.56</v>
+        <v>31278.88</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4845,19 +4845,19 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>REFORÇO QUE SE FAZ DA NE 040-2021 - REF. AO PRIMEIRO TERMO ADITIVO AO CTA 003-2020</t>
+          <t>REFORÇO QUE SE FAZ DA NE 056-2021 - REF. AO TERMO DE CTA Nº 002/2021</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2021NE0000130</t>
+          <t>2021NE0000128</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2/2021</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>31278.88</v>
+        <v>5436.56</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>REFORÇO QUE SE FAZ DA NE 056-2021 - REF. AO TERMO DE CTA Nº 002/2021</t>
+          <t>REFORÇO QUE SE FAZ DA NE 040-2021 - REF. AO PRIMEIRO TERMO ADITIVO AO CTA 003-2020</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2022NE0000015</t>
+          <t>2022NE0000020</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2718.28</v>
+        <v>125919</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB pata atender a CGE.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECILIZADA EM PRESTAÇÃO DE SERVIÇOS DE TI, TIPO DESENVOLVIMENTO DE SISTEMA DE INFORMAÇÃO, LICENÇAS DE USO DE SISTEMA DE INFORMAÇÃO - GESTOR DE CONTEÚDO WEB E LICENÇA DE USO DE</t>
         </is>
       </c>
     </row>
@@ -5002,12 +5002,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2022NE0000020</t>
+          <t>2022NE0000015</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>125919</v>
+        <v>2718.28</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECILIZADA EM PRESTAÇÃO DE SERVIÇOS DE TI, TIPO DESENVOLVIMENTO DE SISTEMA DE INFORMAÇÃO, LICENÇAS DE USO DE SISTEMA DE INFORMAÇÃO - GESTOR DE CONTEÚDO WEB E LICENÇA DE USO DE</t>
+          <t>Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB pata atender a CGE.</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2017NE00150</t>
+          <t>2017NE00147</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1475.29</v>
+        <v>34261.36</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5205,19 +5205,19 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>REFORÇO QUE SE FAZ DA NE Nº 18</t>
+          <t>REFORÇO QUE SE FAZ DA NE 102 - TERMO DE CONTRATO Nº 002/2016</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2017NE00147</t>
+          <t>2017NE00150</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>34261.36</v>
+        <v>1475.29</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5235,14 +5235,14 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>REFORÇO QUE SE FAZ DA NE 102 - TERMO DE CONTRATO Nº 002/2016</t>
+          <t>REFORÇO QUE SE FAZ DA NE Nº 18</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2015NE00077</t>
+          <t>2015NE00076</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>EMPENHO DE SERVIÇO</t>
+          <t>EMPENHO DE SERVIÇOS</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2015NE00076</t>
+          <t>2015NE00077</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>EMPENHO DE SERVIÇOS</t>
+          <t>EMPENHO DE SERVIÇO</t>
         </is>
       </c>
     </row>
@@ -5332,12 +5332,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2024NE0000008</t>
+          <t>2024NE0000003</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>3/2020</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>47748.88</v>
+        <v>2424.2</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE. Demais informações no Projeto Básic</t>
+          <t>Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado -CGE. Demais informações no Projeto Básico, páginas 32 a 35 - SIGED. TC: 0003/2020 AD:</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2024NE0000003</t>
+          <t>2024NE0000008</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>3/2020</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2424.2</v>
+        <v>47748.88</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5415,19 +5415,19 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Contratação de Serviços de Execução do Sistema de Protocolo SPROWEB, para atender a Controladoria Geral do Estado -CGE. Demais informações no Projeto Básico, páginas 32 a 35 - SIGED. TC: 0003/2020 AD:</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Tecnologia da Informação (TI), para atender as necessidades da Controladoria-Geral do Estado - CGE. Demais informações no Projeto Básic</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2020NE00006</t>
+          <t>2020NE00007</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>255877.44</v>
+        <v>27437.2</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada em prestação de serviços de TI, Tipo DESENVOLVIMENTO DE SISTEMA DE INFORMAÇÃO, CONFORME PROJETO BÁSICO .</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Rede, compreendendo o acesso gerenciado à internet através da Rede de Governo, para a CONTROLADORIA-GERAL DO ESTADO.</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5482,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2020NE00007</t>
+          <t>2020NE00006</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>27437.2</v>
+        <v>255877.44</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5505,19 +5505,19 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Rede, compreendendo o acesso gerenciado à internet através da Rede de Governo, para a CONTROLADORIA-GERAL DO ESTADO.</t>
+          <t>Contratação de Empresa Especializada em prestação de serviços de TI, Tipo DESENVOLVIMENTO DE SISTEMA DE INFORMAÇÃO, CONFORME PROJETO BÁSICO .</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2019NE00005</t>
+          <t>2019NE00003</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>21866.7</v>
+        <v>10179.54</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Rede, compreendendo o acesso gerenciado à internet através da Rede de Governo, para a CONTROLADORIA-GERAL DO ESTADO.</t>
+          <t>Contratação de empresa especializada em prestação de Serviços de TI, tipo LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - GESTOR DE CONTEÚDO WEB; e LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - PORTAL DA TRANSP</t>
         </is>
       </c>
     </row>
@@ -5572,12 +5572,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2019NE00003</t>
+          <t>2019NE00005</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>10179.54</v>
+        <v>21866.7</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5595,14 +5595,14 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prestação de Serviços de TI, tipo LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - GESTOR DE CONTEÚDO WEB; e LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - PORTAL DA TRANSP</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Rede, compreendendo o acesso gerenciado à internet através da Rede de Governo, para a CONTROLADORIA-GERAL DO ESTADO.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2018NE00040</t>
+          <t>2018NE00039</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>417481.68</v>
+        <v>34271.38</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2018NE00039</t>
+          <t>2018NE00040</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>34271.38</v>
+        <v>417481.68</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5692,12 +5692,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2017NE00018</t>
+          <t>2017NE00001</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5901.16</v>
+        <v>17130.68</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5715,19 +5715,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇO DE LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, N</t>
+          <t>SERVIÇOS DE REDE COMPREENDENDO DISPONIBILIDADE DE ACESSO A REDE DE GOVERNO COM FORNECIMENTO DE LINK SEGURO DEDICADO PONTO A PONTO ENTRE A REDE DA OUVIDORIA E A PRODAM PARA ACESSO GERENCIADO A INTERNET</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2017NE00001</t>
+          <t>2017NE00018</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>17130.68</v>
+        <v>5901.16</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE REDE COMPREENDENDO DISPONIBILIDADE DE ACESSO A REDE DE GOVERNO COM FORNECIMENTO DE LINK SEGURO DEDICADO PONTO A PONTO ENTRE A REDE DA OUVIDORIA E A PRODAM PARA ACESSO GERENCIADO A INTERNET</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇO DE LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, N</t>
         </is>
       </c>
     </row>
@@ -5782,12 +5782,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2014NE00025</t>
+          <t>2014NE00023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>6/2012</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>432551.76</v>
+        <v>46314</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5805,19 +5805,19 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Contrato No. 2/2013 - Internet 8Mb, Link 3Mb e Servidor Proxy (Subst.Contr 005/2010)</t>
+          <t>Contrato No. 6/2012 - Internet link via satélite de 1 Mbps p.Manacapuru</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2014NE00023</t>
+          <t>2014NE00025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>6/2012</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>46314</v>
+        <v>432551.76</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Contrato No. 6/2012 - Internet link via satélite de 1 Mbps p.Manacapuru</t>
+          <t>Contrato No. 2/2013 - Internet 8Mb, Link 3Mb e Servidor Proxy (Subst.Contr 005/2010)</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2016NE00440</t>
+          <t>2016NE00134</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>17130.68</v>
+        <v>393.03</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5891,19 +5891,19 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Nº TERMO DE CONTRATO Nº 002/2016 - PRESTAÇÃO DE SERVIÇOS DE REDE, COMPREENDENDO A DISPONIBILIDADE DE ACESSO A REDE DE GOVERNO COM O FORNECIMENTO DE LINK SEGURO,</t>
+          <t>4º TA AO CONTRATO Nº 0002/2012-CGE.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2016NE00134</t>
+          <t>2016NE00439</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>393.03</v>
+        <v>2950.58</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5921,19 +5921,19 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>4º TA AO CONTRATO Nº 0002/2012-CGE.</t>
+          <t>REFORÇO QUE SE FAZ PARA EMPENHAR O RESTO DO CONTRATO Nº TERMO DE CONTRATO Nº 007/2016 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇO DE LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO, COMPR</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2016NE00439</t>
+          <t>2016NE00440</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2950.58</v>
+        <v>17130.68</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>REFORÇO QUE SE FAZ PARA EMPENHAR O RESTO DO CONTRATO Nº TERMO DE CONTRATO Nº 007/2016 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇO DE LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO, COMPR</t>
+          <t>Nº TERMO DE CONTRATO Nº 002/2016 - PRESTAÇÃO DE SERVIÇOS DE REDE, COMPREENDENDO A DISPONIBILIDADE DE ACESSO A REDE DE GOVERNO COM O FORNECIMENTO DE LINK SEGURO,</t>
         </is>
       </c>
     </row>
@@ -6018,12 +6018,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2019NE00250</t>
+          <t>2019NE00244</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>23517.6</v>
+        <v>82670.88</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>REFORÇO A NOTA DE EMPENHO Nº 2019NE00087, CORRESPONDENTE AO 4º TRIMESTRE/2019.</t>
+          <t>Reforço da Nota de Empenho 2019NE00004, referente ao 4º Trimestre.</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2019NE00244</t>
+          <t>2019NE00250</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>82670.88</v>
+        <v>23517.6</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6101,28 +6101,24 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Reforço da Nota de Empenho 2019NE00004, referente ao 4º Trimestre.</t>
+          <t>REFORÇO A NOTA DE EMPENHO Nº 2019NE00087, CORRESPONDENTE AO 4º TRIMESTRE/2019.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2017NE00291</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>2/2013</t>
-        </is>
-      </c>
+          <t>2017NE00316</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
         <is>
           <t>01/09/2017</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>8730.879999999999</v>
+        <v>3147.08</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6131,28 +6127,24 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>PAGAMENTO DE EXERCICIO ANTERIOR RD Nº 385/2017 - SERVIÇO DE ACESSO A INTERNET, NF 17238/17239/20986/20987/20988</t>
+          <t>PRORROGAÇÃO DO CONTRATO POR MAIS 12 MESES E REAJUSTE DE PREÇO</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2017NE00292</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>2/2013</t>
-        </is>
-      </c>
+          <t>2017NE00313</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
         <is>
           <t>01/09/2017</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>311368.27</v>
+        <v>17130.68</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6161,7 +6153,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>PAGAMENTO DE EXERCÍCIO ANTERIOR RD Nº 384/2017 - SERVIÇO DE ACESSO A REDE DE INTERNET E SUPORTE TÉCNICO, NFS 15664/14200/14201/14202/15665/15666/14859/14860/14861/14862/14863/14864/15086/15087/15088/1</t>
+          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA DO CONTRATO ORIGINAL POR MAIS 12 MESES.</t>
         </is>
       </c>
     </row>
@@ -6198,17 +6190,21 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2017NE00313</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr"/>
+          <t>2017NE00292</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2/2013</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>01/09/2017</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>17130.68</v>
+        <v>311368.27</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6217,24 +6213,28 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA DO CONTRATO ORIGINAL POR MAIS 12 MESES.</t>
+          <t>PAGAMENTO DE EXERCÍCIO ANTERIOR RD Nº 384/2017 - SERVIÇO DE ACESSO A REDE DE INTERNET E SUPORTE TÉCNICO, NFS 15664/14200/14201/14202/15665/15666/14859/14860/14861/14862/14863/14864/15086/15087/15088/1</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2017NE00316</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
+          <t>2017NE00291</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2/2013</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>01/09/2017</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3147.08</v>
+        <v>8730.879999999999</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6243,21 +6243,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DO CONTRATO POR MAIS 12 MESES E REAJUSTE DE PREÇO</t>
+          <t>PAGAMENTO DE EXERCICIO ANTERIOR RD Nº 385/2017 - SERVIÇO DE ACESSO A INTERNET, NF 17238/17239/20986/20987/20988</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2019NE00173</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00172</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
         <is>
           <t>01/07/2019</t>
@@ -6273,14 +6269,14 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>REFORÇO À NOTA DE EMPENHO Nº 2019NE00003, CORRESPONDENTE AO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 003/2017-CGE.</t>
+          <t>ANULAÇÃO TOTAL PARA AJUSTE NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2019NE00174</t>
+          <t>2019NE00171</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6294,7 +6290,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>124006.32</v>
+        <v>10179.54</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6303,7 +6299,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>REFORÇO À NOTA DE EMPENHO Nº 2019NE00003, CORRESPONDENTE AO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 003/2017-CGE.</t>
+          <t>Contratação de empresa especializada em prestação de Serviços de TI, tipo LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - GESTOR DE CONTEÚDO WEB; e LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - PORTAL DA TRANSP</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6336,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2019NE00171</t>
+          <t>2019NE00174</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6354,7 +6350,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>10179.54</v>
+        <v>124006.32</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6363,17 +6359,21 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em prestação de Serviços de TI, tipo LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - GESTOR DE CONTEÚDO WEB; e LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO - PORTAL DA TRANSP</t>
+          <t>REFORÇO À NOTA DE EMPENHO Nº 2019NE00003, CORRESPONDENTE AO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 003/2017-CGE.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2019NE00172</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
+          <t>2019NE00173</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C201" t="inlineStr">
         <is>
           <t>01/07/2019</t>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL PARA AJUSTE NA DESCRIÇÃO.</t>
+          <t>REFORÇO À NOTA DE EMPENHO Nº 2019NE00003, CORRESPONDENTE AO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 003/2017-CGE.</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2015NE00346</t>
+          <t>2015NE00362</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>TERCEIRO TERMO ADITIVO AO CONTRATO Nº 006/2012 - PRESTAÇÃO DOS SERVIÇOS DE ACESSO A REDE MUNDIAL INTERNET NO PAC MANACAPURU.</t>
+          <t>ANULAÇÃO QUE SE FAZ PARA CORREÇÃO DA DESCRIÇÃO Nº DA PORTARIA.</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2015NE00362</t>
+          <t>2015NE00346</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>ANULAÇÃO QUE SE FAZ PARA CORREÇÃO DA DESCRIÇÃO Nº DA PORTARIA.</t>
+          <t>TERCEIRO TERMO ADITIVO AO CONTRATO Nº 006/2012 - PRESTAÇÃO DOS SERVIÇOS DE ACESSO A REDE MUNDIAL INTERNET NO PAC MANACAPURU.</t>
         </is>
       </c>
     </row>
@@ -6546,12 +6546,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2016NE00326</t>
+          <t>2016NE00325</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>25696.02</v>
+        <v>4425.87</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6569,19 +6569,19 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇOS DE REDE, COMPREENDENDO A DISPONIBILIDADE DE ACESSO A REDE DE GOVERNO COM O FORNECIMENTO DE LINK SEGURO, DEDICADO, PONTO A PONTO ENTRE A SEDE DA OUVIDORIA E A PRODAM, PARA ACESSO </t>
+          <t>REFORÇO QUE SE FAZ PARA EMPENHAR O RESTO DO CONTRATO Nº TERMO DE CONTRATO Nº 007/2016 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇO DE LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO, COMPR</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2016NE00325</t>
+          <t>2016NE00326</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>4425.87</v>
+        <v>25696.02</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>REFORÇO QUE SE FAZ PARA EMPENHAR O RESTO DO CONTRATO Nº TERMO DE CONTRATO Nº 007/2016 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇO DE LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO, COMPR</t>
+          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇOS DE REDE, COMPREENDENDO A DISPONIBILIDADE DE ACESSO A REDE DE GOVERNO COM O FORNECIMENTO DE LINK SEGURO, DEDICADO, PONTO A PONTO ENTRE A SEDE DA OUVIDORIA E A PRODAM, PARA ACESSO </t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2017NE00102</t>
+          <t>2017NE00107</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>17130.68</v>
+        <v>8565.34</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA DO CONTRATO ORIGINAL POR MAIS 12 MESES.</t>
+          <t>PAGAMENTO DE EXERCÍCIO ANTERIOR RD Nº 015/2017 - SERVIÇO DE REDE MUNDIAL, ACESSO A METROMAO E SERVIÇOS DE FIREWALL, MÊS 12/2016, NF 20986/20987/20988 EMITIDAS EM 01/12/2016</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2017NE00107</t>
+          <t>2017NE00102</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>8565.34</v>
+        <v>17130.68</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6715,24 +6715,28 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>PAGAMENTO DE EXERCÍCIO ANTERIOR RD Nº 015/2017 - SERVIÇO DE REDE MUNDIAL, ACESSO A METROMAO E SERVIÇOS DE FIREWALL, MÊS 12/2016, NF 20986/20987/20988 EMITIDAS EM 01/12/2016</t>
+          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA DO CONTRATO ORIGINAL POR MAIS 12 MESES.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2016NE00147</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr"/>
+          <t>2016NE00149</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C213" t="inlineStr">
         <is>
           <t>01/03/2016</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>42826.7</v>
+        <v>34261.36</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6741,28 +6745,24 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>ANULAÇÃO QUE SE FAZ PARA CORREÇÃO DE DATA</t>
+          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇOS DE REDE, COMPREENDENDO A DISPONIBILIDADE DE ACESSO A REDE DE GOVERNO COM O FORNECIMENTO DE LINK SEGURO, DEDICADO, PONTO A PONTO ENTRE A SEDE DA OUVIDORIA E A PRODAM, PARA ACESSO </t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2016NE00149</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2016NE00147</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
           <t>01/03/2016</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>34261.36</v>
+        <v>42826.7</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇOS DE REDE, COMPREENDENDO A DISPONIBILIDADE DE ACESSO A REDE DE GOVERNO COM O FORNECIMENTO DE LINK SEGURO, DEDICADO, PONTO A PONTO ENTRE A SEDE DA OUVIDORIA E A PRODAM, PARA ACESSO </t>
+          <t>ANULAÇÃO QUE SE FAZ PARA CORREÇÃO DE DATA</t>
         </is>
       </c>
     </row>
